--- a/balance/source/balance-data.xlsx
+++ b/balance/source/balance-data.xlsx
@@ -171,7 +171,7 @@
         <v>5.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -182,10 +182,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>20.0</v>
+        <v>200.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -196,10 +196,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>30.0</v>
+        <v>300.0</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -210,10 +210,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>40.0</v>
+        <v>400.0</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>0.0</v>
@@ -224,10 +224,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>50.0</v>
+        <v>500.0</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>0.0</v>
@@ -238,10 +238,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>60.0</v>
+        <v>600.0</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>0.0</v>
@@ -252,10 +252,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>5.0</v>
+        <v>35.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>70.0</v>
+        <v>700.0</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -266,10 +266,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>5.0</v>
+        <v>40.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>80.0</v>
+        <v>800.0</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>0.0</v>
@@ -280,10 +280,10 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>5.0</v>
+        <v>45.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>90.0</v>
+        <v>900.0</v>
       </c>
       <c r="D10" t="n" s="0">
         <v>0.0</v>
@@ -294,13 +294,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>150.0</v>
+        <v>1000.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="12">
@@ -308,13 +308,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>10.0</v>
+        <v>55.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>165.0</v>
+        <v>1100.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="13">
@@ -322,13 +322,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>10.0</v>
+        <v>60.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>180.0</v>
+        <v>1200.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="14">
@@ -336,13 +336,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>10.0</v>
+        <v>65.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>195.0</v>
+        <v>1300.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="15">
@@ -350,13 +350,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>1400.0</v>
+      </c>
+      <c r="D15" t="n" s="0">
         <v>10.0</v>
-      </c>
-      <c r="C15" t="n" s="0">
-        <v>210.0</v>
-      </c>
-      <c r="D15" t="n" s="0">
-        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -364,13 +364,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>10.0</v>
+        <v>75.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>225.0</v>
+        <v>1500.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="17">
@@ -378,13 +378,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>10.0</v>
+        <v>80.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>240.0</v>
+        <v>1600.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="18">
@@ -392,13 +392,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>10.0</v>
+        <v>85.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>255.0</v>
+        <v>1700.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="19">
@@ -406,13 +406,13 @@
         <v>18.0</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>10.0</v>
+        <v>90.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>270.0</v>
+        <v>1800.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="20">
@@ -420,13 +420,13 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>10.0</v>
+        <v>95.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>285.0</v>
+        <v>1900.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="21">
@@ -434,13 +434,13 @@
         <v>20.0</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>15.0</v>
+        <v>100.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>400.0</v>
+        <v>2000.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="22">
@@ -448,13 +448,13 @@
         <v>21.0</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>15.0</v>
+        <v>105.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>420.0</v>
+        <v>2100.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>1.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="23">
@@ -462,13 +462,13 @@
         <v>22.0</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>15.0</v>
+        <v>110.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>440.0</v>
+        <v>2200.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>1.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="24">
@@ -476,13 +476,13 @@
         <v>23.0</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>15.0</v>
+        <v>115.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>460.0</v>
+        <v>2300.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>1.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="25">
@@ -490,13 +490,13 @@
         <v>24.0</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>15.0</v>
+        <v>120.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>480.0</v>
+        <v>2400.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="26">
@@ -504,13 +504,13 @@
         <v>25.0</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>15.0</v>
+        <v>125.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>500.0</v>
+        <v>2500.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>1.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="27">
@@ -518,13 +518,13 @@
         <v>26.0</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>15.0</v>
+        <v>130.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>520.0</v>
+        <v>2600.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>1.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="28">
@@ -532,13 +532,13 @@
         <v>27.0</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>15.0</v>
+        <v>135.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>540.0</v>
+        <v>2700.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>1.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="29">
@@ -546,13 +546,13 @@
         <v>28.0</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>15.0</v>
+        <v>140.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>560.0</v>
+        <v>2800.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>1.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="30">
@@ -560,13 +560,13 @@
         <v>29.0</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>15.0</v>
+        <v>145.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>580.0</v>
+        <v>2900.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="31">
@@ -574,13 +574,13 @@
         <v>30.0</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>20.0</v>
+        <v>150.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>900.0</v>
+        <v>3000.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>2.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="32">
@@ -588,13 +588,13 @@
         <v>31.0</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>20.0</v>
+        <v>155.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>930.0</v>
+        <v>3100.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="33">
@@ -602,13 +602,13 @@
         <v>32.0</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>20.0</v>
+        <v>160.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>960.0</v>
+        <v>3200.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>2.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="34">
@@ -616,13 +616,13 @@
         <v>33.0</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>20.0</v>
+        <v>165.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>990.0</v>
+        <v>3300.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>2.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="35">
@@ -630,13 +630,13 @@
         <v>34.0</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>20.0</v>
+        <v>170.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>1020.0</v>
+        <v>3400.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>2.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="36">
@@ -644,13 +644,13 @@
         <v>35.0</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>20.0</v>
+        <v>175.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>1050.0</v>
+        <v>3500.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>2.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="37">
@@ -658,13 +658,13 @@
         <v>36.0</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>20.0</v>
+        <v>180.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>1080.0</v>
+        <v>3600.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>2.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="38">
@@ -672,13 +672,13 @@
         <v>37.0</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>20.0</v>
+        <v>185.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>1110.0</v>
+        <v>3700.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>2.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="39">
@@ -686,13 +686,13 @@
         <v>38.0</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>20.0</v>
+        <v>190.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>1140.0</v>
+        <v>3800.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>2.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="40">
@@ -700,13 +700,13 @@
         <v>39.0</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>20.0</v>
+        <v>195.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>1170.0</v>
+        <v>3900.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>2.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="41">
@@ -714,13 +714,13 @@
         <v>40.0</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>30.0</v>
+        <v>200.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>1600.0</v>
+        <v>4000.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>3.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="42">
@@ -728,13 +728,13 @@
         <v>41.0</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>30.0</v>
+        <v>205.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>1640.0</v>
+        <v>4100.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>3.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="43">
@@ -742,13 +742,13 @@
         <v>42.0</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>30.0</v>
+        <v>210.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>1680.0</v>
+        <v>4200.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>3.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="44">
@@ -756,13 +756,13 @@
         <v>43.0</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>30.0</v>
+        <v>215.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>1720.0</v>
+        <v>4300.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>3.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="45">
@@ -770,13 +770,13 @@
         <v>44.0</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>30.0</v>
+        <v>220.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>1760.0</v>
+        <v>4400.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>3.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="46">
@@ -784,13 +784,13 @@
         <v>45.0</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>30.0</v>
+        <v>225.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>1800.0</v>
+        <v>4500.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>3.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="47">
@@ -798,13 +798,13 @@
         <v>46.0</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>30.0</v>
+        <v>230.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>1840.0</v>
+        <v>4600.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>3.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="48">
@@ -812,13 +812,13 @@
         <v>47.0</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>30.0</v>
+        <v>235.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>1880.0</v>
+        <v>4700.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>3.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="49">
@@ -826,13 +826,13 @@
         <v>48.0</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>30.0</v>
+        <v>240.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>1920.0</v>
+        <v>4800.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>3.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="50">
@@ -840,13 +840,13 @@
         <v>49.0</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>30.0</v>
+        <v>245.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>1960.0</v>
+        <v>4900.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>3.0</v>
+        <v>80.0</v>
       </c>
     </row>
   </sheetData>

--- a/balance/source/balance-data.xlsx
+++ b/balance/source/balance-data.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Config" r:id="rId3" sheetId="1"/>
     <sheet name="GameReward" r:id="rId4" sheetId="2"/>
     <sheet name="AlienUpgrade" r:id="rId5" sheetId="3"/>
+    <sheet name="AlienSpec" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="62">
   <si>
     <t>key</t>
   </si>
@@ -44,6 +45,162 @@
   </si>
   <si>
     <t>requiredGrowthCell</t>
+  </si>
+  <si>
+    <t>alienId</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>baseAttack</t>
+  </si>
+  <si>
+    <t>baseMp</t>
+  </si>
+  <si>
+    <t>attackSpeed</t>
+  </si>
+  <si>
+    <t>attackRange</t>
+  </si>
+  <si>
+    <t>evolutionTargetId</t>
+  </si>
+  <si>
+    <t>isLocked</t>
+  </si>
+  <si>
+    <t>LEGEND 1</t>
+  </si>
+  <si>
+    <t>LEGEND 등급의 강력한 왹져입니다.</t>
+  </si>
+  <si>
+    <t>LEGEND</t>
+  </si>
+  <si>
+    <t>LEGEND 2</t>
+  </si>
+  <si>
+    <t>LEGEND 3</t>
+  </si>
+  <si>
+    <t>LEGEND 4</t>
+  </si>
+  <si>
+    <t>LEGEND 5</t>
+  </si>
+  <si>
+    <t>LEGEND 6</t>
+  </si>
+  <si>
+    <t>LEGEND 7</t>
+  </si>
+  <si>
+    <t>UNIQUE 1</t>
+  </si>
+  <si>
+    <t>UNIQUE 등급의 강력한 왹져입니다.</t>
+  </si>
+  <si>
+    <t>UNIQUE</t>
+  </si>
+  <si>
+    <t>UNIQUE 2</t>
+  </si>
+  <si>
+    <t>UNIQUE 3</t>
+  </si>
+  <si>
+    <t>UNIQUE 4</t>
+  </si>
+  <si>
+    <t>UNIQUE 5</t>
+  </si>
+  <si>
+    <t>UNIQUE 6</t>
+  </si>
+  <si>
+    <t>UNIQUE 7</t>
+  </si>
+  <si>
+    <t>EPIC 1</t>
+  </si>
+  <si>
+    <t>EPIC 등급의 강력한 왹져입니다.</t>
+  </si>
+  <si>
+    <t>EPIC</t>
+  </si>
+  <si>
+    <t>EPIC 2</t>
+  </si>
+  <si>
+    <t>EPIC 3</t>
+  </si>
+  <si>
+    <t>EPIC 4</t>
+  </si>
+  <si>
+    <t>EPIC 5</t>
+  </si>
+  <si>
+    <t>EPIC 6</t>
+  </si>
+  <si>
+    <t>EPIC 7</t>
+  </si>
+  <si>
+    <t>NORMAL 1</t>
+  </si>
+  <si>
+    <t>NORMAL 등급의 강력한 왹져입니다.</t>
+  </si>
+  <si>
+    <t>NORMAL</t>
+  </si>
+  <si>
+    <t>NORMAL 2</t>
+  </si>
+  <si>
+    <t>NORMAL 3</t>
+  </si>
+  <si>
+    <t>NORMAL 4</t>
+  </si>
+  <si>
+    <t>NORMAL 5</t>
+  </si>
+  <si>
+    <t>NORMAL 6</t>
+  </si>
+  <si>
+    <t>NORMAL 7</t>
+  </si>
+  <si>
+    <t>MYTHIC 1</t>
+  </si>
+  <si>
+    <t>MYTHIC 등급의 강력한 왹져입니다.</t>
+  </si>
+  <si>
+    <t>MYTHIC</t>
+  </si>
+  <si>
+    <t>MYTHIC 2</t>
+  </si>
+  <si>
+    <t>MYTHIC 3</t>
+  </si>
+  <si>
+    <t>MYTHIC 4</t>
   </si>
 </sst>
 </file>
@@ -852,4 +1009,1048 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="G2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H2" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I2" s="0"/>
+      <c r="J2" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H3" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I3" s="0"/>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I4" s="0"/>
+      <c r="J4" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H5" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I5" s="0"/>
+      <c r="J5" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H6" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I6" s="0"/>
+      <c r="J6" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H7" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I7" s="0"/>
+      <c r="J7" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H8" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I8" s="0"/>
+      <c r="J8" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>250.0</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H9" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="J9" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>250.0</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H10" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="J10" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>250.0</v>
+      </c>
+      <c r="G11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H11" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J11" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>250.0</v>
+      </c>
+      <c r="G12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H12" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="J12" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E13" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>250.0</v>
+      </c>
+      <c r="G13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H13" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="J13" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E14" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="F14" t="n" s="0">
+        <v>250.0</v>
+      </c>
+      <c r="G14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H14" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="J14" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E15" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="F15" t="n" s="0">
+        <v>250.0</v>
+      </c>
+      <c r="G15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H15" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="J15" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E16" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="F16" t="n" s="0">
+        <v>150.0</v>
+      </c>
+      <c r="G16" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H16" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="J16" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E17" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="F17" t="n" s="0">
+        <v>150.0</v>
+      </c>
+      <c r="G17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H17" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="J17" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E18" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="F18" t="n" s="0">
+        <v>150.0</v>
+      </c>
+      <c r="G18" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H18" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="J18" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E19" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="F19" t="n" s="0">
+        <v>150.0</v>
+      </c>
+      <c r="G19" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H19" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="J19" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E20" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="F20" t="n" s="0">
+        <v>150.0</v>
+      </c>
+      <c r="G20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H20" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="J20" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E21" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="F21" t="n" s="0">
+        <v>150.0</v>
+      </c>
+      <c r="G21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H21" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="J21" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E22" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="F22" t="n" s="0">
+        <v>150.0</v>
+      </c>
+      <c r="G22" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H22" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="J22" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E23" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F23" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="G23" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H23" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I23" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="J23" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E24" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F24" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="G24" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H24" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I24" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="J24" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E25" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F25" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="G25" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H25" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I25" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="J25" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E26" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F26" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="G26" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H26" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I26" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="J26" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E27" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F27" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="G27" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H27" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I27" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="J27" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E28" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F28" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="G28" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H28" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I28" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="J28" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E29" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F29" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="G29" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H29" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I29" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="J29" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E30" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F30" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="G30" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H30" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I30" s="0"/>
+      <c r="J30" t="b" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E31" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F31" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="G31" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H31" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I31" s="0"/>
+      <c r="J31" t="b" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n" s="0">
+        <v>31.0</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E32" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F32" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="G32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H32" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I32" s="0"/>
+      <c r="J32" t="b" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n" s="0">
+        <v>32.0</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E33" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="F33" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="G33" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H33" t="n" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="I33" s="0"/>
+      <c r="J33" t="b" s="0">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/balance/source/balance-data.xlsx
+++ b/balance/source/balance-data.xlsx
@@ -10,12 +10,14 @@
     <sheet name="GameReward" r:id="rId4" sheetId="2"/>
     <sheet name="AlienUpgrade" r:id="rId5" sheetId="3"/>
     <sheet name="AlienSpec" r:id="rId6" sheetId="4"/>
+    <sheet name="ShopProduct" r:id="rId7" sheetId="5"/>
+    <sheet name="GachaPool" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="85">
   <si>
     <t>key</t>
   </si>
@@ -201,6 +203,75 @@
   </si>
   <si>
     <t>MYTHIC 4</t>
+  </si>
+  <si>
+    <t>productId</t>
+  </si>
+  <si>
+    <t>currencyType</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>drawCount</t>
+  </si>
+  <si>
+    <t>gachaPoolId</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>ALIEN_GACHA_SINGLE</t>
+  </si>
+  <si>
+    <t>왹져 1회 뽑기</t>
+  </si>
+  <si>
+    <t>DIAMOND</t>
+  </si>
+  <si>
+    <t>STANDARD_ALIEN_POOL</t>
+  </si>
+  <si>
+    <t>ALIEN_GACHA_TEN</t>
+  </si>
+  <si>
+    <t>왹져 10회 연속 뽑기</t>
+  </si>
+  <si>
+    <t>poolId</t>
+  </si>
+  <si>
+    <t>poolName</t>
+  </si>
+  <si>
+    <t>poolActive</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>alienIds</t>
+  </si>
+  <si>
+    <t>일반 왹져 소환</t>
+  </si>
+  <si>
+    <t>22,23,24,25,26,27,28</t>
+  </si>
+  <si>
+    <t>15,16,17,18,19,20,21</t>
+  </si>
+  <si>
+    <t>8,9,10,11,12,13,14</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7</t>
+  </si>
+  <si>
+    <t>29,30,31,32</t>
   </si>
 </sst>
 </file>
@@ -2053,4 +2124,213 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="G2" t="b" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C2" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>6000.0</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>2800.0</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>900.0</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C5" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>250.0</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C6" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/balance/source/balance-data.xlsx
+++ b/balance/source/balance-data.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="1" r:id="R33e9aa93656e481f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="Ra81d5d87ab524ed6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgrade" sheetId="3" r:id="R820bd38efc084c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="Rb441ce62e47341ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="R407490e05d764c03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="Rf32a3eca6e3b4ec8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="R71ab8b29e48d4a7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="Rbd75ee90cdac476e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="1" r:id="Rf4b66af997dc4e85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="Rd0e3fa8e82b74c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgrade" sheetId="3" r:id="R5b224f5603ff4b6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="Rcab1e37ebf554216"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="R3258be8d797d4938"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="Rf9b1ab501ea644ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="R46e967ef77854a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="R1192f71603044b70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,196 +77,85 @@
     <x:t xml:space="preserve">isLocked</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">LEGEND 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LEGEND 등급의 강력한 왹져입니다.</x:t>
+    <x:t xml:space="preserve">productId</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">currencyType</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">price</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">drawCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">gachaPoolId</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">active</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALIEN_GACHA_SINGLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">왹져 1회 뽑기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DIAMOND</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">STANDARD_ALIEN_POOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALIEN_GACHA_TEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">왹져 10회 연속 뽑기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">poolId</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">poolName</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">poolActive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">weight</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">alienIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">일반 왹져 소환</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">NORMAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22,23,24,25,26,27,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EPIC</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">15,16,17,18,19,20,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">UNIQUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">8,9,10,11,12,13,14</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">LEGEND</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">LEGEND 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LEGEND 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LEGEND 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LEGEND 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LEGEND 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LEGEND 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNIQUE 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNIQUE 등급의 강력한 왹져입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNIQUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNIQUE 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNIQUE 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNIQUE 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNIQUE 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNIQUE 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNIQUE 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EPIC 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EPIC 등급의 강력한 왹져입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EPIC</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EPIC 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EPIC 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EPIC 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EPIC 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EPIC 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EPIC 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL 등급의 강력한 왹져입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MYTHIC 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MYTHIC 등급의 강력한 왹져입니다.</x:t>
+    <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">MYTHIC</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MYTHIC 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MYTHIC 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MYTHIC 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">productId</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">currencyType</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">price</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">drawCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">gachaPoolId</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">active</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALIEN_GACHA_SINGLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">왹져 1회 뽑기</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIAMOND</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STANDARD_ALIEN_POOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALIEN_GACHA_TEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">왹져 10회 연속 뽑기</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">poolId</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">poolName</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">poolActive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">weight</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">alienIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">일반 왹져 소환</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22,23,24,25,26,27,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">15,16,17,18,19,20,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">8,9,10,11,12,13,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1,2,3,4,5,6,7</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">29,30,31,32</x:t>
@@ -301,15 +190,39 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1306,1003 +1219,1483 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="n">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="B2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D2" t="s">
-        <x:v>22</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>LEGEND 1</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>LEGEND 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>LEGEND</x:v>
       </x:c>
       <x:c r="E2" t="n">
-        <x:v>50.0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F2" t="n">
-        <x:v>500.0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H2" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I2"/>
-      <x:c r="J2" t="b">
+      <x:c r="J2" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="n">
-        <x:v>2.0</x:v>
-      </x:c>
-      <x:c r="B3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D3" t="s">
-        <x:v>22</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>LEGEND 2</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>LEGEND 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>LEGEND</x:v>
       </x:c>
       <x:c r="E3" t="n">
-        <x:v>50.0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F3" t="n">
-        <x:v>500.0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G3" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H3" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I3"/>
-      <x:c r="J3" t="b">
+      <x:c r="J3" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="n">
-        <x:v>3.0</x:v>
-      </x:c>
-      <x:c r="B4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C4" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D4" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>LEGEND 3</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>LEGEND 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>LEGEND</x:v>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>50.0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>500.0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G4" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H4" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I4"/>
-      <x:c r="J4" t="b">
+      <x:c r="J4" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="n">
-        <x:v>4.0</x:v>
-      </x:c>
-      <x:c r="B5" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C5" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D5" t="s">
-        <x:v>22</x:v>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>LEGEND 4</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>LEGEND 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>LEGEND</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>50.0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>500.0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G5" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I5"/>
-      <x:c r="J5" t="b">
+      <x:c r="J5" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="n">
-        <x:v>5.0</x:v>
-      </x:c>
-      <x:c r="B6" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C6" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D6" t="s">
-        <x:v>22</x:v>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>LEGEND 5</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>LEGEND 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>LEGEND</x:v>
       </x:c>
       <x:c r="E6" t="n">
-        <x:v>50.0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F6" t="n">
-        <x:v>500.0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G6" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H6" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I6"/>
-      <x:c r="J6" t="b">
+      <x:c r="J6" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="n">
-        <x:v>6.0</x:v>
-      </x:c>
-      <x:c r="B7" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D7" t="s">
-        <x:v>22</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>LEGEND 6</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>LEGEND 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>LEGEND</x:v>
       </x:c>
       <x:c r="E7" t="n">
-        <x:v>50.0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>500.0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G7" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H7" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I7"/>
-      <x:c r="J7" t="b">
+      <x:c r="J7" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="n">
-        <x:v>7.0</x:v>
-      </x:c>
-      <x:c r="B8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D8" t="s">
-        <x:v>22</x:v>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>LEGEND 7</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>LEGEND 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>LEGEND</x:v>
       </x:c>
       <x:c r="E8" t="n">
-        <x:v>50.0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F8" t="n">
-        <x:v>500.0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G8" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I8"/>
-      <x:c r="J8" t="b">
+      <x:c r="J8" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="n">
-        <x:v>8.0</x:v>
-      </x:c>
-      <x:c r="B9" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C9" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D9" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>UNIQUE 1</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>UNIQUE 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>UNIQUE</x:v>
       </x:c>
       <x:c r="E9" t="n">
-        <x:v>25.0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>250.0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G9" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H9" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I9" t="n">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="J9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="n">
-        <x:v>9.0</x:v>
-      </x:c>
-      <x:c r="B10" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C10" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D10" t="s">
-        <x:v>31</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>UNIQUE 2</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>UNIQUE 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>UNIQUE</x:v>
       </x:c>
       <x:c r="E10" t="n">
-        <x:v>25.0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F10" t="n">
-        <x:v>250.0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G10" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H10" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I10" t="n">
-        <x:v>2.0</x:v>
-      </x:c>
-      <x:c r="J10" t="b">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="n">
-        <x:v>10.0</x:v>
-      </x:c>
-      <x:c r="B11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>UNIQUE 3</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>UNIQUE 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>UNIQUE</x:v>
       </x:c>
       <x:c r="E11" t="n">
-        <x:v>25.0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F11" t="n">
-        <x:v>250.0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G11" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H11" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I11" t="n">
-        <x:v>3.0</x:v>
-      </x:c>
-      <x:c r="J11" t="b">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="n">
-        <x:v>11.0</x:v>
-      </x:c>
-      <x:c r="B12" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D12" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>UNIQUE 4</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>UNIQUE 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>UNIQUE</x:v>
       </x:c>
       <x:c r="E12" t="n">
-        <x:v>25.0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F12" t="n">
-        <x:v>250.0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G12" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H12" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I12" t="n">
-        <x:v>4.0</x:v>
-      </x:c>
-      <x:c r="J12" t="b">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="n">
-        <x:v>12.0</x:v>
-      </x:c>
-      <x:c r="B13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D13" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>UNIQUE 5</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>UNIQUE 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>UNIQUE</x:v>
       </x:c>
       <x:c r="E13" t="n">
-        <x:v>25.0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F13" t="n">
-        <x:v>250.0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G13" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H13" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I13" t="n">
-        <x:v>5.0</x:v>
-      </x:c>
-      <x:c r="J13" t="b">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="n">
-        <x:v>13.0</x:v>
-      </x:c>
-      <x:c r="B14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D14" t="s">
-        <x:v>31</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>UNIQUE 6</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>UNIQUE 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>UNIQUE</x:v>
       </x:c>
       <x:c r="E14" t="n">
-        <x:v>25.0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F14" t="n">
-        <x:v>250.0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G14" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H14" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I14" t="n">
-        <x:v>6.0</x:v>
-      </x:c>
-      <x:c r="J14" t="b">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="n">
-        <x:v>14.0</x:v>
-      </x:c>
-      <x:c r="B15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D15" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>UNIQUE 7</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>UNIQUE 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>UNIQUE</x:v>
       </x:c>
       <x:c r="E15" t="n">
-        <x:v>25.0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F15" t="n">
-        <x:v>250.0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G15" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H15" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I15" t="n">
-        <x:v>7.0</x:v>
-      </x:c>
-      <x:c r="J15" t="b">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J15" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="n">
-        <x:v>15.0</x:v>
-      </x:c>
-      <x:c r="B16" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D16" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>EPIC 1</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>EPIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>EPIC</x:v>
       </x:c>
       <x:c r="E16" t="n">
-        <x:v>15.0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F16" t="n">
-        <x:v>150.0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G16" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H16" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I16" t="n">
-        <x:v>8.0</x:v>
-      </x:c>
-      <x:c r="J16" t="b">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="n">
-        <x:v>16.0</x:v>
-      </x:c>
-      <x:c r="B17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D17" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>EPIC 2</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>EPIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>EPIC</x:v>
       </x:c>
       <x:c r="E17" t="n">
-        <x:v>15.0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F17" t="n">
-        <x:v>150.0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G17" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H17" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I17" t="n">
-        <x:v>9.0</x:v>
-      </x:c>
-      <x:c r="J17" t="b">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J17" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="n">
-        <x:v>17.0</x:v>
-      </x:c>
-      <x:c r="B18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C18" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D18" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>EPIC 3</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>EPIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>EPIC</x:v>
       </x:c>
       <x:c r="E18" t="n">
-        <x:v>15.0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F18" t="n">
-        <x:v>150.0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G18" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H18" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I18" t="n">
-        <x:v>10.0</x:v>
-      </x:c>
-      <x:c r="J18" t="b">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J18" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="n">
-        <x:v>18.0</x:v>
-      </x:c>
-      <x:c r="B19" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C19" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D19" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>EPIC 4</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>EPIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>EPIC</x:v>
       </x:c>
       <x:c r="E19" t="n">
-        <x:v>15.0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F19" t="n">
-        <x:v>150.0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G19" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H19" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I19" t="n">
-        <x:v>11.0</x:v>
-      </x:c>
-      <x:c r="J19" t="b">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J19" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="n">
-        <x:v>19.0</x:v>
-      </x:c>
-      <x:c r="B20" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C20" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D20" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>EPIC 5</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>EPIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>EPIC</x:v>
       </x:c>
       <x:c r="E20" t="n">
-        <x:v>15.0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F20" t="n">
-        <x:v>150.0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G20" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H20" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I20" t="n">
-        <x:v>12.0</x:v>
-      </x:c>
-      <x:c r="J20" t="b">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J20" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="n">
-        <x:v>20.0</x:v>
-      </x:c>
-      <x:c r="B21" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C21" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D21" t="s">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>EPIC 6</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>EPIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>EPIC</x:v>
       </x:c>
       <x:c r="E21" t="n">
-        <x:v>15.0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F21" t="n">
-        <x:v>150.0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G21" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H21" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I21" t="n">
-        <x:v>13.0</x:v>
-      </x:c>
-      <x:c r="J21" t="b">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J21" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="n">
-        <x:v>21.0</x:v>
-      </x:c>
-      <x:c r="B22" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C22" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D22" t="s">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>EPIC 7</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>EPIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>EPIC</x:v>
       </x:c>
       <x:c r="E22" t="n">
-        <x:v>15.0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F22" t="n">
-        <x:v>150.0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G22" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H22" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I22" t="n">
-        <x:v>14.0</x:v>
-      </x:c>
-      <x:c r="J22" t="b">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J22" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="n">
-        <x:v>22.0</x:v>
-      </x:c>
-      <x:c r="B23" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C23" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D23" t="s">
-        <x:v>49</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>NORMAL 1</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>NORMAL 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>NORMAL</x:v>
       </x:c>
       <x:c r="E23" t="n">
-        <x:v>10.0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F23" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G23" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H23" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I23" t="n">
-        <x:v>15.0</x:v>
-      </x:c>
-      <x:c r="J23" t="b">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J23" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="n">
-        <x:v>23.0</x:v>
-      </x:c>
-      <x:c r="B24" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C24" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D24" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>NORMAL 2</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>NORMAL 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>NORMAL</x:v>
       </x:c>
       <x:c r="E24" t="n">
-        <x:v>10.0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F24" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G24" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H24" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I24" t="n">
-        <x:v>16.0</x:v>
-      </x:c>
-      <x:c r="J24" t="b">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J24" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="n">
-        <x:v>24.0</x:v>
-      </x:c>
-      <x:c r="B25" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C25" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D25" t="s">
-        <x:v>49</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>NORMAL 3</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>NORMAL 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>NORMAL</x:v>
       </x:c>
       <x:c r="E25" t="n">
-        <x:v>10.0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F25" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G25" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H25" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I25" t="n">
-        <x:v>17.0</x:v>
-      </x:c>
-      <x:c r="J25" t="b">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J25" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="n">
-        <x:v>25.0</x:v>
-      </x:c>
-      <x:c r="B26" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C26" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D26" t="s">
-        <x:v>49</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>NORMAL 4</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>NORMAL 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>NORMAL</x:v>
       </x:c>
       <x:c r="E26" t="n">
-        <x:v>10.0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F26" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G26" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H26" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I26" t="n">
-        <x:v>18.0</x:v>
-      </x:c>
-      <x:c r="J26" t="b">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="n">
-        <x:v>26.0</x:v>
-      </x:c>
-      <x:c r="B27" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C27" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D27" t="s">
-        <x:v>49</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>NORMAL 5</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>NORMAL 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>NORMAL</x:v>
       </x:c>
       <x:c r="E27" t="n">
-        <x:v>10.0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F27" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G27" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H27" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I27" t="n">
-        <x:v>19.0</x:v>
-      </x:c>
-      <x:c r="J27" t="b">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="n">
-        <x:v>27.0</x:v>
-      </x:c>
-      <x:c r="B28" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C28" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D28" t="s">
-        <x:v>49</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>NORMAL 6</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>NORMAL 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>NORMAL</x:v>
       </x:c>
       <x:c r="E28" t="n">
-        <x:v>10.0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F28" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G28" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H28" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I28" t="n">
-        <x:v>20.0</x:v>
-      </x:c>
-      <x:c r="J28" t="b">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="n">
-        <x:v>28.0</x:v>
-      </x:c>
-      <x:c r="B29" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C29" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D29" t="s">
-        <x:v>49</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>NORMAL 7</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>NORMAL 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>NORMAL</x:v>
       </x:c>
       <x:c r="E29" t="n">
-        <x:v>10.0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F29" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G29" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H29" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I29" t="n">
-        <x:v>21.0</x:v>
-      </x:c>
-      <x:c r="J29" t="b">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J29" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="n">
-        <x:v>29.0</x:v>
-      </x:c>
-      <x:c r="B30" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C30" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D30" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>MYTHIC 1</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>MYTHIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>MYTHIC</x:v>
       </x:c>
       <x:c r="E30" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F30" t="n">
-        <x:v>1000.0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G30" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H30" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I30"/>
-      <x:c r="J30" t="b">
-        <x:v>1</x:v>
+      <x:c r="J30" s="3" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="n">
-        <x:v>30.0</x:v>
-      </x:c>
-      <x:c r="B31" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C31" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D31" t="s">
-        <x:v>58</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>MYTHIC 2</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>MYTHIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>MYTHIC</x:v>
       </x:c>
       <x:c r="E31" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F31" t="n">
-        <x:v>1000.0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G31" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H31" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I31"/>
-      <x:c r="J31" t="b">
-        <x:v>1</x:v>
+      <x:c r="J31" s="3" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="n">
-        <x:v>31.0</x:v>
-      </x:c>
-      <x:c r="B32" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C32" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D32" t="s">
-        <x:v>58</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>MYTHIC 3</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>MYTHIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>MYTHIC</x:v>
       </x:c>
       <x:c r="E32" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F32" t="n">
-        <x:v>1000.0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G32" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H32" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I32"/>
-      <x:c r="J32" t="b">
-        <x:v>1</x:v>
+      <x:c r="J32" s="3" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="n">
-        <x:v>32.0</x:v>
-      </x:c>
-      <x:c r="B33" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C33" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D33" t="s">
-        <x:v>58</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>MYTHIC 4</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>MYTHIC 등급의 강력한 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>MYTHIC</x:v>
       </x:c>
       <x:c r="E33" t="n">
-        <x:v>100.0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F33" t="n">
-        <x:v>1000.0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G33" t="n">
-        <x:v>1.0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H33" t="n">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="I33"/>
-      <x:c r="J33" t="b">
+      <x:c r="J33" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>MYTHIC 5</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E34" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F34" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H34" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I34"/>
+      <x:c r="J34" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>MYTHIC 6</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E35" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F35" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I35"/>
+      <x:c r="J35" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>MYTHIC 7</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E36" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F36" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H36" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I36"/>
+      <x:c r="J36" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>MYTHIC 8</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E37" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F37" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H37" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I37"/>
+      <x:c r="J37" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>MYTHIC 9</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I38"/>
+      <x:c r="J38" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>MYTHIC 10</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I39"/>
+      <x:c r="J39" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>MYTHIC 11</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I40"/>
+      <x:c r="J40" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>MYTHIC 12</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I41"/>
+      <x:c r="J41" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>MYTHIC 13</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I42"/>
+      <x:c r="J42" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>MYTHIC 14</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I43"/>
+      <x:c r="J43" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>MYTHIC 15</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I44"/>
+      <x:c r="J44" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>MYTHIC 16</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I45"/>
+      <x:c r="J45" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>MYTHIC 17</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I46"/>
+      <x:c r="J46" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>MYTHIC 18</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I47"/>
+      <x:c r="J47" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>MYTHIC 19</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E48" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F48" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G48" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H48" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I48"/>
+      <x:c r="J48" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>MYTHIC 20</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>출시 예정 신화 왹져입니다.</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="E49" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F49" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H49" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I49"/>
+      <x:c r="J49" s="3" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2317,36 +2710,36 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
-        <x:v>62</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>63</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>65</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>66</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>67</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="s">
-        <x:v>68</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>69</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C2" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D2" t="n">
         <x:v>500.0</x:v>
@@ -2355,7 +2748,7 @@
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="F2" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G2" t="b">
         <x:v>1</x:v>
@@ -2363,13 +2756,13 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>73</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D3" t="n">
         <x:v>5000.0</x:v>
@@ -2378,7 +2771,7 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" t="b">
         <x:v>1</x:v>
@@ -2395,50 +2788,50 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
-        <x:v>74</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>75</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>76</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D1" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>77</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>78</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D2" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E2" t="n">
         <x:v>6000.0</x:v>
       </x:c>
       <x:c r="F2" t="s">
-        <x:v>80</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C3" t="b">
         <x:v>1</x:v>
@@ -2450,67 +2843,67 @@
         <x:v>2800.0</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>81</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C4" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E4" t="n">
         <x:v>900.0</x:v>
       </x:c>
       <x:c r="F4" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C5" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" t="s">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E5" t="n">
         <x:v>250.0</x:v>
       </x:c>
       <x:c r="F5" t="s">
-        <x:v>83</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C6" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E6" t="n">
         <x:v>50.0</x:v>
       </x:c>
       <x:c r="F6" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/balance/source/balance-data.xlsx
+++ b/balance/source/balance-data.xlsx
@@ -2,12 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="R0bd10ed205284a5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="R8f9ba37337824c9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="Rde0ec609798b49c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="R6ceddbafc4aa4882"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="R7119c2f69cf7469e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="R00a27212cbf1490e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="Ra288a389c45b46ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="Ra7301815bb974dcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="R07287466c5fc47a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="Rfd9ab43137924ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="Rad80e8e0cfff4412"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="Rcf4fa68c1c7c4792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterSpec" sheetId="9" r:id="R9990c8a81f184db0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="10" r:id="R61aa011dd85b41bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="11" r:id="Rbac3bdfdf8de4faa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldLimitBalance" sheetId="12" r:id="R131e8aee660143fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonBalance" sheetId="13" r:id="Ra564ff342848498b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MergeRule" sheetId="14" r:id="R7955defd62114a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicChoiceBalance" sheetId="15" r:id="R8fea9b0c63504d3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -146,32 +153,287 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:color indexed="8"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="darkGray"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="16">
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -424,6 +686,355 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="20" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>modeId</x:v>
+      </x:c>
+      <x:c r="B1" s="16" t="str">
+        <x:v>playerCount</x:v>
+      </x:c>
+      <x:c r="C1" s="16" t="str">
+        <x:v>maxAliveMonsterCountPerField</x:v>
+      </x:c>
+      <x:c r="D1" s="16" t="str">
+        <x:v>warningThreshold</x:v>
+      </x:c>
+      <x:c r="E1" s="17" t="str">
+        <x:v>dangerThreshold</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="20" customHeight="1">
+      <x:c r="A2" s="39" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B2" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C2" s="40" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D2" s="40" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E2" s="41" t="n">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="20" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>modeId</x:v>
+      </x:c>
+      <x:c r="B1" s="16" t="str">
+        <x:v>summonType</x:v>
+      </x:c>
+      <x:c r="C1" s="16" t="str">
+        <x:v>baseCost</x:v>
+      </x:c>
+      <x:c r="D1" s="16" t="str">
+        <x:v>costIncreasePerUse</x:v>
+      </x:c>
+      <x:c r="E1" s="16" t="str">
+        <x:v>maxUses</x:v>
+      </x:c>
+      <x:c r="F1" s="16" t="str">
+        <x:v>resultPoolId</x:v>
+      </x:c>
+      <x:c r="G1" s="17" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="20" customHeight="1">
+      <x:c r="A2" s="39" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B2" s="40" t="str">
+        <x:v>KIDNAP</x:v>
+      </x:c>
+      <x:c r="C2" s="40" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D2" s="40" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E2" s="40" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F2" s="40" t="str">
+        <x:v>STANDARD_SUMMON_POOL</x:v>
+      </x:c>
+      <x:c r="G2" s="42" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="20" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>sourceGrade</x:v>
+      </x:c>
+      <x:c r="B1" s="16" t="str">
+        <x:v>requiredCount</x:v>
+      </x:c>
+      <x:c r="C1" s="16" t="str">
+        <x:v>sameSpeciesRequired</x:v>
+      </x:c>
+      <x:c r="D1" s="16" t="str">
+        <x:v>resultType</x:v>
+      </x:c>
+      <x:c r="E1" s="16" t="str">
+        <x:v>resultGrade</x:v>
+      </x:c>
+      <x:c r="F1" s="17" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="20" customHeight="1">
+      <x:c r="A2" s="18" t="str">
+        <x:v>NORMAL</x:v>
+      </x:c>
+      <x:c r="B2" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C2" s="33" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="19" t="str">
+        <x:v>RANDOM_NEXT_GRADE</x:v>
+      </x:c>
+      <x:c r="E2" s="19" t="str">
+        <x:v>EPIC</x:v>
+      </x:c>
+      <x:c r="F2" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="20" customHeight="1">
+      <x:c r="A3" s="21" t="str">
+        <x:v>EPIC</x:v>
+      </x:c>
+      <x:c r="B3" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="22" t="str">
+        <x:v>RANDOM_NEXT_GRADE</x:v>
+      </x:c>
+      <x:c r="E3" s="22" t="str">
+        <x:v>UNIQUE</x:v>
+      </x:c>
+      <x:c r="F3" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="20" customHeight="1">
+      <x:c r="A4" s="21" t="str">
+        <x:v>UNIQUE</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C4" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" s="22" t="str">
+        <x:v>RANDOM_NEXT_GRADE</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
+        <x:v>LEGEND</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="20" customHeight="1">
+      <x:c r="A5" s="21" t="str">
+        <x:v>LEGEND</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>MYTHIC_CHOICE</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="F5" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="20" customHeight="1">
+      <x:c r="A6" s="24" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="B6" s="25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="35" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" s="25" t="str">
+        <x:v>DISABLED</x:v>
+      </x:c>
+      <x:c r="E6" s="25" t="str">
+        <x:v>MYTHIC</x:v>
+      </x:c>
+      <x:c r="F6" s="26" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="A2:A100">
+      <x:formula1>"NORMAL,EPIC,UNIQUE,LEGEND,MYTHIC"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D2:D100">
+      <x:formula1>"RANDOM_NEXT_GRADE,MYTHIC_CHOICE,DISABLED"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="20" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>modeId</x:v>
+      </x:c>
+      <x:c r="B1" s="16" t="str">
+        <x:v>candidateCount</x:v>
+      </x:c>
+      <x:c r="C1" s="16" t="str">
+        <x:v>freeRerollCount</x:v>
+      </x:c>
+      <x:c r="D1" s="16" t="str">
+        <x:v>paidRerollLimit</x:v>
+      </x:c>
+      <x:c r="E1" s="16" t="str">
+        <x:v>paidRerollCost</x:v>
+      </x:c>
+      <x:c r="F1" s="16" t="str">
+        <x:v>excludePreviousCandidates</x:v>
+      </x:c>
+      <x:c r="G1" s="16" t="str">
+        <x:v>selectionTimeoutSeconds</x:v>
+      </x:c>
+      <x:c r="H1" s="16" t="str">
+        <x:v>autoSelectPolicy</x:v>
+      </x:c>
+      <x:c r="I1" s="16" t="str">
+        <x:v>battleContinuesDuringSelection</x:v>
+      </x:c>
+      <x:c r="J1" s="17" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="20" customHeight="1">
+      <x:c r="A2" s="39" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B2" s="40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C2" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="40" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F2" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="40" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H2" s="40" t="str">
+        <x:v>FIRST</x:v>
+      </x:c>
+      <x:c r="I2" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" s="42" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="H2:H100">
+      <x:formula1>"FIRST,RANDOM"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -3901,4 +4512,746 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="20" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>monsterId</x:v>
+      </x:c>
+      <x:c r="B1" s="16" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="C1" s="16" t="str">
+        <x:v>monsterType</x:v>
+      </x:c>
+      <x:c r="D1" s="16" t="str">
+        <x:v>baseHp</x:v>
+      </x:c>
+      <x:c r="E1" s="16" t="str">
+        <x:v>moveSpeed</x:v>
+      </x:c>
+      <x:c r="F1" s="16" t="str">
+        <x:v>killGold</x:v>
+      </x:c>
+      <x:c r="G1" s="17" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="20" customHeight="1">
+      <x:c r="A2" s="18" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="B2" s="19" t="str">
+        <x:v>Normal Monster</x:v>
+      </x:c>
+      <x:c r="C2" s="19" t="str">
+        <x:v>NORMAL</x:v>
+      </x:c>
+      <x:c r="D2" s="27" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E2" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F2" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G2" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="20" customHeight="1">
+      <x:c r="A3" s="21" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="B3" s="22" t="str">
+        <x:v>Elite Monster</x:v>
+      </x:c>
+      <x:c r="C3" s="22" t="str">
+        <x:v>ELITE</x:v>
+      </x:c>
+      <x:c r="D3" s="28" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E3" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F3" s="31" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G3" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="20" customHeight="1">
+      <x:c r="A4" s="24" t="str">
+        <x:v>WAVE_BOSS</x:v>
+      </x:c>
+      <x:c r="B4" s="25" t="str">
+        <x:v>Wave Boss</x:v>
+      </x:c>
+      <x:c r="C4" s="25" t="str">
+        <x:v>WAVE_BOSS</x:v>
+      </x:c>
+      <x:c r="D4" s="29" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E4" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F4" s="32" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G4" s="26" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="C2:C100">
+      <x:formula1>"NORMAL,ELITE,WAVE_BOSS"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="20" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>modeId</x:v>
+      </x:c>
+      <x:c r="B1" s="16" t="str">
+        <x:v>wave</x:v>
+      </x:c>
+      <x:c r="C1" s="16" t="str">
+        <x:v>hpMultiplier</x:v>
+      </x:c>
+      <x:c r="D1" s="16" t="str">
+        <x:v>interWaveDelaySeconds</x:v>
+      </x:c>
+      <x:c r="E1" s="16" t="str">
+        <x:v>isBossWave</x:v>
+      </x:c>
+      <x:c r="F1" s="16" t="str">
+        <x:v>bossTimeLimitSeconds</x:v>
+      </x:c>
+      <x:c r="G1" s="16" t="str">
+        <x:v>spawnGroupId</x:v>
+      </x:c>
+      <x:c r="H1" s="17" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="20" customHeight="1">
+      <x:c r="A2" s="18" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B2" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E2" s="33" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2" s="19" t="str">
+        <x:v>WAVE_01</x:v>
+      </x:c>
+      <x:c r="H2" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="20" customHeight="1">
+      <x:c r="A3" s="21" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B3" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="28" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="D3" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E3" s="34" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F3" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G3" s="22" t="str">
+        <x:v>WAVE_02</x:v>
+      </x:c>
+      <x:c r="H3" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="20" customHeight="1">
+      <x:c r="A4" s="21" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B4" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C4" s="28" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="D4" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E4" s="34" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="str">
+        <x:v>WAVE_03</x:v>
+      </x:c>
+      <x:c r="H4" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="20" customHeight="1">
+      <x:c r="A5" s="21" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B5" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="34" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="22" t="str">
+        <x:v>WAVE_04</x:v>
+      </x:c>
+      <x:c r="H5" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="20" customHeight="1">
+      <x:c r="A6" s="21" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B6" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="28" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="D6" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="34" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="22" t="str">
+        <x:v>WAVE_05</x:v>
+      </x:c>
+      <x:c r="H6" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="20" customHeight="1">
+      <x:c r="A7" s="21" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B7" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C7" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D7" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="34" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="22" t="str">
+        <x:v>WAVE_06</x:v>
+      </x:c>
+      <x:c r="H7" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="20" customHeight="1">
+      <x:c r="A8" s="21" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B8" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C8" s="28" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="D8" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="22" t="str">
+        <x:v>WAVE_07</x:v>
+      </x:c>
+      <x:c r="H8" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="20" customHeight="1">
+      <x:c r="A9" s="21" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="28" t="n">
+        <x:v>1.7000000000000002</x:v>
+      </x:c>
+      <x:c r="D9" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="str">
+        <x:v>WAVE_08</x:v>
+      </x:c>
+      <x:c r="H9" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="20" customHeight="1">
+      <x:c r="A10" s="21" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B10" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C10" s="28" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="34" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="22" t="str">
+        <x:v>WAVE_09</x:v>
+      </x:c>
+      <x:c r="H10" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="20" customHeight="1">
+      <x:c r="A11" s="24" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B11" s="32" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="D11" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="35" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="25" t="str">
+        <x:v>WAVE_10_BOSS</x:v>
+      </x:c>
+      <x:c r="H11" s="26" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="20" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>spawnGroupId</x:v>
+      </x:c>
+      <x:c r="B1" s="16" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="C1" s="16" t="str">
+        <x:v>monsterId</x:v>
+      </x:c>
+      <x:c r="D1" s="16" t="str">
+        <x:v>spawnCountPerField</x:v>
+      </x:c>
+      <x:c r="E1" s="16" t="str">
+        <x:v>startDelaySeconds</x:v>
+      </x:c>
+      <x:c r="F1" s="16" t="str">
+        <x:v>spawnIntervalSeconds</x:v>
+      </x:c>
+      <x:c r="G1" s="17" t="str">
+        <x:v>lanePolicy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="20" customHeight="1">
+      <x:c r="A2" s="18" t="str">
+        <x:v>WAVE_01</x:v>
+      </x:c>
+      <x:c r="B2" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="19" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="D2" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E2" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="36" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="20" customHeight="1">
+      <x:c r="A3" s="21" t="str">
+        <x:v>WAVE_02</x:v>
+      </x:c>
+      <x:c r="B3" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="22" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="D3" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E3" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F3" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G3" s="37" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="20" customHeight="1">
+      <x:c r="A4" s="21" t="str">
+        <x:v>WAVE_03</x:v>
+      </x:c>
+      <x:c r="B4" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="D4" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E4" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G4" s="37" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="20" customHeight="1">
+      <x:c r="A5" s="21" t="str">
+        <x:v>WAVE_04</x:v>
+      </x:c>
+      <x:c r="B5" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="D5" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" s="37" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="20" customHeight="1">
+      <x:c r="A6" s="21" t="str">
+        <x:v>WAVE_05</x:v>
+      </x:c>
+      <x:c r="B6" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="22" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="D6" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E6" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="37" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="20" customHeight="1">
+      <x:c r="A7" s="21" t="str">
+        <x:v>WAVE_05</x:v>
+      </x:c>
+      <x:c r="B7" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="22" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="D7" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E7" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="37" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="20" customHeight="1">
+      <x:c r="A8" s="21" t="str">
+        <x:v>WAVE_06</x:v>
+      </x:c>
+      <x:c r="B8" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="22" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E8" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="37" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="20" customHeight="1">
+      <x:c r="A9" s="21" t="str">
+        <x:v>WAVE_07</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E9" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="37" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="20" customHeight="1">
+      <x:c r="A10" s="21" t="str">
+        <x:v>WAVE_08</x:v>
+      </x:c>
+      <x:c r="B10" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E10" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="37" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="20" customHeight="1">
+      <x:c r="A11" s="21" t="str">
+        <x:v>WAVE_08</x:v>
+      </x:c>
+      <x:c r="B11" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E11" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F11" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="37" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="20" customHeight="1">
+      <x:c r="A12" s="21" t="str">
+        <x:v>WAVE_09</x:v>
+      </x:c>
+      <x:c r="B12" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E12" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="37" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="20" customHeight="1">
+      <x:c r="A13" s="24" t="str">
+        <x:v>WAVE_10_BOSS</x:v>
+      </x:c>
+      <x:c r="B13" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="str">
+        <x:v>WAVE_BOSS</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="38" t="str">
+        <x:v>EACH_FIELD</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="G2:G100">
+      <x:formula1>"EACH_FIELD"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/balance/source/balance-data.xlsx
+++ b/balance/source/balance-data.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="Ra288a389c45b46ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="Ra7301815bb974dcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="R07287466c5fc47a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="Rfd9ab43137924ed3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="Rad80e8e0cfff4412"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="Rcf4fa68c1c7c4792"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterSpec" sheetId="9" r:id="R9990c8a81f184db0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="10" r:id="R61aa011dd85b41bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="11" r:id="Rbac3bdfdf8de4faa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldLimitBalance" sheetId="12" r:id="R131e8aee660143fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonBalance" sheetId="13" r:id="Ra564ff342848498b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MergeRule" sheetId="14" r:id="R7955defd62114a8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicChoiceBalance" sheetId="15" r:id="R8fea9b0c63504d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="R3153ae779b45407a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="R19d624c3f3894fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="Rb523f60aa88b4d31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="R96a97c75a2664393"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="R2d5547afeb0f4ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="R0c76181f0f614cd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterSpec" sheetId="9" r:id="R6f4765bf5ac44495"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="10" r:id="Rb817b1c31418414c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="11" r:id="Refa36199e3b1496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldLimitBalance" sheetId="12" r:id="R81cf21f4820146ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonBalance" sheetId="13" r:id="R7d4240beb4d74584"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MergeRule" sheetId="14" r:id="Ra1c9ed527a77460b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicChoiceBalance" sheetId="15" r:id="R72628e842292402d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5243,7 +5243,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="38" t="str">
-        <x:v>EACH_FIELD</x:v>
+        <x:v>BOSS_SHARED</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/balance/source/balance-data.xlsx
+++ b/balance/source/balance-data.xlsx
@@ -2,19 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="R3153ae779b45407a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="R19d624c3f3894fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="Rb523f60aa88b4d31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="R96a97c75a2664393"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="R2d5547afeb0f4ffa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="R0c76181f0f614cd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterSpec" sheetId="9" r:id="R6f4765bf5ac44495"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="10" r:id="Rb817b1c31418414c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="11" r:id="Refa36199e3b1496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldLimitBalance" sheetId="12" r:id="R81cf21f4820146ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonBalance" sheetId="13" r:id="R7d4240beb4d74584"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MergeRule" sheetId="14" r:id="Ra1c9ed527a77460b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicChoiceBalance" sheetId="15" r:id="R72628e842292402d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="R9b14419f2da14f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="Rd0f7ba4deb654124"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="R3d00f7a079ee4548"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="Rd48c38ca230a4792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="R6cad4f97cc1445dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="R97770bfa885a44c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterSpec" sheetId="9" r:id="R2d5bed8725c049fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="10" r:id="R447b6fd78fed4c2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="11" r:id="R46e5c628606043ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldLimitBalance" sheetId="12" r:id="R4ba20093862945ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonBalance" sheetId="13" r:id="Rfe5a8b856e474dc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MergeRule" sheetId="14" r:id="Rdd8f4287aab940cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicChoiceBalance" sheetId="15" r:id="Re960bbabad0d43e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonPool" sheetId="16" r:id="R93af79aabd8b433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MutationSpec" sheetId="17" r:id="R01c24ca822964bc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MutationConfig" sheetId="18" r:id="Rc78619a872564b43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InjectorPool" sheetId="19" r:id="R985dde127a2d4bc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleReward" sheetId="20" r:id="Ra29de3f1096b4353"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -149,9 +154,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.00"/>
+    <x:numFmt numFmtId="202" formatCode="#,##0"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -166,12 +172,22 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="darkGray"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -323,7 +339,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="44">
+  <x:cellXfs count="53">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -440,6 +456,21 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -462,6 +493,24 @@
     </xfpb:a>
   </xfpb:bag>
 </xfpb:FeaturePropertyBags>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BattleRewardTable" displayName="BattleRewardTable" ref="A1:J19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="rewardType"/>
+    <x:tableColumn id="2" name="mapId"/>
+    <x:tableColumn id="3" name="wave"/>
+    <x:tableColumn id="4" name="gold"/>
+    <x:tableColumn id="5" name="universalPiece"/>
+    <x:tableColumn id="6" name="diamond"/>
+    <x:tableColumn id="7" name="failureRewardBaseGold"/>
+    <x:tableColumn id="8" name="failureRewardCapPercent"/>
+    <x:tableColumn id="9" name="minimumRewardWave"/>
+    <x:tableColumn id="10" name="enabled"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1013,7 +1062,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="40" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H2" s="40" t="str">
         <x:v>FIRST</x:v>
@@ -1032,6 +1081,1222 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="5.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16.3799991607666" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>poolId</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>poolName</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>poolActive</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>grade</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>weight</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>alienIds</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>STANDARD_SUMMON_POOL</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>Battle Kidnap NORMAL</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>NORMAL</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>22,23,24,25,26,27,28</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>mutationType</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+      <x:c r="C1" s="46" t="str">
+        <x:v>injectorEnabled</x:v>
+      </x:c>
+      <x:c r="D1" s="46" t="str">
+        <x:v>randomActivationEnabled</x:v>
+      </x:c>
+      <x:c r="E1" s="46" t="str">
+        <x:v>weight</x:v>
+      </x:c>
+      <x:c r="F1" s="46" t="str">
+        <x:v>attackMultiplier</x:v>
+      </x:c>
+      <x:c r="G1" s="46" t="str">
+        <x:v>mpMultiplier</x:v>
+      </x:c>
+      <x:c r="H1" s="46" t="str">
+        <x:v>attackSpeedMultiplier</x:v>
+      </x:c>
+      <x:c r="I1" s="46" t="str">
+        <x:v>rangeMultiplier</x:v>
+      </x:c>
+      <x:c r="J1" s="46" t="str">
+        <x:v>goldMultiplier</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="22" t="str">
+        <x:v>BERSERK</x:v>
+      </x:c>
+      <x:c r="B2" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" s="22" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="G2" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I2" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="22" t="str">
+        <x:v>GREEDY</x:v>
+      </x:c>
+      <x:c r="B3" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E3" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G3" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I3" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="22" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="22" t="str">
+        <x:v>SWIFT</x:v>
+      </x:c>
+      <x:c r="B4" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="22" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="I4" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J4" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="22" t="str">
+        <x:v>GIANT</x:v>
+      </x:c>
+      <x:c r="B5" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="G5" s="22" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="H5" s="22" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="I5" s="22" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="J5" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="22" t="str">
+        <x:v>OBESE</x:v>
+      </x:c>
+      <x:c r="B6" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="22" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="G6" s="22" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="H6" s="22" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I6" s="22" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="J6" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="22" t="str">
+        <x:v>TOXIC</x:v>
+      </x:c>
+      <x:c r="B7" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F7" s="22" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G7" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I7" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J7" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="22" t="str">
+        <x:v>FROZEN</x:v>
+      </x:c>
+      <x:c r="B8" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F8" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="22" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="H8" s="22" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="I8" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>BLANK</x:v>
+      </x:c>
+      <x:c r="B9" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="45" t="str">
+        <x:v>modeId</x:v>
+      </x:c>
+      <x:c r="B1" s="45" t="str">
+        <x:v>initialActivationCost</x:v>
+      </x:c>
+      <x:c r="C1" s="45" t="str">
+        <x:v>rerollCost1</x:v>
+      </x:c>
+      <x:c r="D1" s="45" t="str">
+        <x:v>rerollCost2</x:v>
+      </x:c>
+      <x:c r="E1" s="45" t="str">
+        <x:v>rerollCost3</x:v>
+      </x:c>
+      <x:c r="F1" s="45" t="str">
+        <x:v>rerollCost4</x:v>
+      </x:c>
+      <x:c r="G1" s="45" t="str">
+        <x:v>rerollCostAfterMax</x:v>
+      </x:c>
+      <x:c r="H1" s="45" t="str">
+        <x:v>injectorReplaceCost</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COOP_STANDARD</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="G2" t="n">
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="H2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="45" t="str">
+        <x:v>poolId</x:v>
+      </x:c>
+      <x:c r="B1" s="45" t="str">
+        <x:v>poolName</x:v>
+      </x:c>
+      <x:c r="C1" s="45" t="str">
+        <x:v>poolActive</x:v>
+      </x:c>
+      <x:c r="D1" s="45" t="str">
+        <x:v>mutationType</x:v>
+      </x:c>
+      <x:c r="E1" s="45" t="str">
+        <x:v>weight</x:v>
+      </x:c>
+      <x:c r="F1" s="45" t="str">
+        <x:v>resultType</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>BATTLE_INJECTOR_POOL</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>Battle Kidnap Injector</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>BERSERK</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>MUTATION_INJECTOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>BATTLE_INJECTOR_POOL</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Battle Kidnap Injector</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>GREEDY</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>MUTATION_INJECTOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>BATTLE_INJECTOR_POOL</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Battle Kidnap Injector</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>SWIFT</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>MUTATION_INJECTOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>BATTLE_INJECTOR_POOL</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Battle Kidnap Injector</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>GIANT</x:v>
+      </x:c>
+      <x:c r="E5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>MUTATION_INJECTOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>BATTLE_INJECTOR_POOL</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Battle Kidnap Injector</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>OBESE</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>MUTATION_INJECTOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>BATTLE_INJECTOR_POOL</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Battle Kidnap Injector</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>TOXIC</x:v>
+      </x:c>
+      <x:c r="E7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>MUTATION_INJECTOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>BATTLE_INJECTOR_POOL</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Battle Kidnap Injector</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>FROZEN</x:v>
+      </x:c>
+      <x:c r="E8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>MUTATION_INJECTOR</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="4.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="4.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="19.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="6.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="51" t="str">
+        <x:v>rewardType</x:v>
+      </x:c>
+      <x:c r="B1" s="51" t="str">
+        <x:v>mapId</x:v>
+      </x:c>
+      <x:c r="C1" s="51" t="str">
+        <x:v>wave</x:v>
+      </x:c>
+      <x:c r="D1" s="51" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E1" s="51" t="str">
+        <x:v>universalPiece</x:v>
+      </x:c>
+      <x:c r="F1" s="51" t="str">
+        <x:v>diamond</x:v>
+      </x:c>
+      <x:c r="G1" s="51" t="str">
+        <x:v>failureRewardBaseGold</x:v>
+      </x:c>
+      <x:c r="H1" s="51" t="str">
+        <x:v>failureRewardCapPercent</x:v>
+      </x:c>
+      <x:c r="I1" s="51" t="str">
+        <x:v>minimumRewardWave</x:v>
+      </x:c>
+      <x:c r="J1" s="51" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="22" t="str">
+        <x:v>CONFIG</x:v>
+      </x:c>
+      <x:c r="B2" s="22" t="str">
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="C2" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D2" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2" s="52" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="H2" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="I2" s="52" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J2" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="22" t="str">
+        <x:v>CHECKPOINT</x:v>
+      </x:c>
+      <x:c r="B3" s="22" t="str">
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J3" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="22" t="str">
+        <x:v>CHECKPOINT</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="str">
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="C4" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D4" s="52" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="E4" s="52" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H4" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I4" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J4" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="22" t="str">
+        <x:v>CHECKPOINT</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="C5" s="52" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D5" s="52" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E5" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F5" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I5" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J5" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="22" t="str">
+        <x:v>CHECKPOINT</x:v>
+      </x:c>
+      <x:c r="B6" s="22" t="str">
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="C6" s="52" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D6" s="52" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="E6" s="52" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F6" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="22" t="str">
+        <x:v>CHECKPOINT</x:v>
+      </x:c>
+      <x:c r="B7" s="22" t="str">
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="C7" s="52" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D7" s="52" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="E7" s="52" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F7" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="22" t="str">
+        <x:v>CHECKPOINT</x:v>
+      </x:c>
+      <x:c r="B8" s="22" t="str">
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="C8" s="52" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D8" s="52" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="E8" s="52" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F8" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="22" t="str">
+        <x:v>CHECKPOINT</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="C9" s="52" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D9" s="52" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="E9" s="52" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F9" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="22" t="str">
+        <x:v>CHECKPOINT</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="C10" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D10" s="52" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="E10" s="52" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F10" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="22" t="str">
+        <x:v>MAP_FIRST_CLEAR</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>NEPTUNE</x:v>
+      </x:c>
+      <x:c r="C11" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D11" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="52" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="G11" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="22" t="str">
+        <x:v>MAP_FIRST_CLEAR</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>URANUS</x:v>
+      </x:c>
+      <x:c r="C12" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D12" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="52" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="G12" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="22" t="str">
+        <x:v>MAP_FIRST_CLEAR</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>SATURN</x:v>
+      </x:c>
+      <x:c r="C13" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D13" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="52" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="G13" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="22" t="str">
+        <x:v>MAP_FIRST_CLEAR</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>JUPITER</x:v>
+      </x:c>
+      <x:c r="C14" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D14" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="52" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="G14" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="22" t="str">
+        <x:v>MAP_FIRST_CLEAR</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>MARS</x:v>
+      </x:c>
+      <x:c r="C15" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D15" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="52" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="G15" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="22" t="str">
+        <x:v>MAP_FIRST_CLEAR</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:v>EARTH</x:v>
+      </x:c>
+      <x:c r="C16" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D16" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="52" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="G16" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="22" t="str">
+        <x:v>MAP_FIRST_CLEAR</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="str">
+        <x:v>VENUS</x:v>
+      </x:c>
+      <x:c r="C17" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D17" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="52" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="G17" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="22" t="str">
+        <x:v>MAP_FIRST_CLEAR</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>MERCURY</x:v>
+      </x:c>
+      <x:c r="C18" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D18" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="52" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="G18" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="22" t="str">
+        <x:v>MAP_FIRST_CLEAR</x:v>
+      </x:c>
+      <x:c r="B19" s="22" t="str">
+        <x:v>SUN</x:v>
+      </x:c>
+      <x:c r="C19" s="52" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D19" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="52" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="G19" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3911c28d19242ab"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 

--- a/balance/source/balance-data.xlsx
+++ b/balance/source/balance-data.xlsx
@@ -2,30 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="R203f81c69fa7420a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="R955dfb33cdff4d87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="R8159b09e6fea42af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="R754641a3992847c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="R3ade59e324d14fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="R4eef95b0f041498e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterSpec" sheetId="9" r:id="R0c423b9f1f744e5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="10" r:id="Rc4cd56d7b90e4e2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="11" r:id="R1f6ea0b216d44942"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldLimitBalance" sheetId="12" r:id="R7916f0c5e64443af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonBalance" sheetId="13" r:id="R8836f0bf29fe4474"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MergeRule" sheetId="14" r:id="Rc3a4e720ba5949ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicChoiceBalance" sheetId="15" r:id="Rf1c9e5fc877f446d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonPool" sheetId="16" r:id="Rbdc9b657e4e7428c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MutationSpec" sheetId="17" r:id="Rd5b863d2f58543c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MutationConfig" sheetId="18" r:id="R3fad9033996943c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InjectorPool" sheetId="19" r:id="Rcf100d419e1b4499"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleReward" sheetId="20" r:id="R717b6374d1d3485e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResonanceBalance" sheetId="21" r:id="R68f4ddff07944c75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanetBattle" sheetId="22" r:id="R8a0bac7c951a42b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingConfig" sheetId="23" r:id="R606589274b814921"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingResult" sheetId="24" r:id="R9406269998e84537"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingRecipe" sheetId="25" r:id="R002839e3e76a41a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BreedingCombinationPublic" sheetId="26" r:id="Rc1c21977b1f14494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="Rcacfa28437c043d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="Rc278cef287d846df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="R60984770b4164b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="R74e840a342754e42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="R246729d0e97a423e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="R9c7d13cbc2404bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterSpec" sheetId="9" r:id="R403b49043f1f4a38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="10" r:id="R12a8803b5ae849f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="11" r:id="R08338be293e047c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldLimitBalance" sheetId="12" r:id="R401c20ea27474009"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonBalance" sheetId="13" r:id="R617e6784a14341f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MergeRule" sheetId="14" r:id="R20bcb4333ff04a3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicChoiceBalance" sheetId="15" r:id="Rb07f10bb0941488c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonPool" sheetId="16" r:id="Rbc01fc2091a149aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MutationSpec" sheetId="17" r:id="Rd919f9e71da54f3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MutationConfig" sheetId="18" r:id="Rc0d18afb71f241f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InjectorPool" sheetId="19" r:id="R48586e5b60d143e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleReward" sheetId="20" r:id="Rc0dd1101f1d74f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResonanceBalance" sheetId="21" r:id="R33d9aaefca5c4866"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanetBattle" sheetId="22" r:id="Rd36380ed3d6a4659"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingConfig" sheetId="23" r:id="Recdc977ced8f4b83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingResult" sheetId="24" r:id="Raafc5d4d20d84fc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingRecipe" sheetId="25" r:id="R3cbc87f5427f4a1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BreedingCombinationPublic" sheetId="26" r:id="Rec7430fa07764765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyContent" sheetId="27" r:id="R11200e515fc141f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -208,7 +209,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="18">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -293,6 +294,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3B5B7A"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -530,7 +536,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="140">
+  <x:cellXfs count="156">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -859,6 +865,65 @@
     <x:xf numFmtId="0" fontId="6" fillId="17" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -896,6 +961,19 @@
     <x:tableColumn id="8" name="failureRewardCapPercent"/>
     <x:tableColumn id="9" name="minimumRewardWave"/>
     <x:tableColumn id="10" name="enabled"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DailyContentTable" displayName="DailyContentTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="contentType"/>
+    <x:tableColumn id="2" name="stage"/>
+    <x:tableColumn id="3" name="repeatReward"/>
+    <x:tableColumn id="4" name="firstClearReward"/>
+    <x:tableColumn id="5" name="enabled"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -3059,7 +3137,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1b37ab6002142c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R209cfc00e12d4f21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19541,6 +19619,212 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="4.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="147" t="str">
+        <x:v>contentType</x:v>
+      </x:c>
+      <x:c r="B1" s="148" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="C1" s="148" t="str">
+        <x:v>repeatReward</x:v>
+      </x:c>
+      <x:c r="D1" s="148" t="str">
+        <x:v>firstClearReward</x:v>
+      </x:c>
+      <x:c r="E1" s="149" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="150" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B2" s="151" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="151" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D2" s="151" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E2" s="152" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="150" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B3" s="151" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="151" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D3" s="151" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E3" s="152" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="150" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B4" s="151" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C4" s="151" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D4" s="151" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E4" s="152" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="150" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B5" s="151" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="151" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D5" s="151" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E5" s="152" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="150" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B6" s="151" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="151" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D6" s="151" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E6" s="152" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="150" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B7" s="151" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="151" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="151" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="152" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="150" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B8" s="151" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C8" s="151" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="151" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E8" s="152" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="150" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B9" s="151" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C9" s="151" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D9" s="151" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E9" s="152" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="150" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B10" s="151" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="151" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D10" s="151" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E10" s="152" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="153" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B11" s="154" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C11" s="154" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="154" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="155" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra244cf70bf03403a"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>

--- a/balance/source/balance-data.xlsx
+++ b/balance/source/balance-data.xlsx
@@ -2,31 +2,32 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="Rcacfa28437c043d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="Rc278cef287d846df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="R60984770b4164b2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="R74e840a342754e42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="R246729d0e97a423e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="R9c7d13cbc2404bff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterSpec" sheetId="9" r:id="R403b49043f1f4a38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="10" r:id="R12a8803b5ae849f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="11" r:id="R08338be293e047c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldLimitBalance" sheetId="12" r:id="R401c20ea27474009"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonBalance" sheetId="13" r:id="R617e6784a14341f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MergeRule" sheetId="14" r:id="R20bcb4333ff04a3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicChoiceBalance" sheetId="15" r:id="Rb07f10bb0941488c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonPool" sheetId="16" r:id="Rbc01fc2091a149aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MutationSpec" sheetId="17" r:id="Rd919f9e71da54f3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MutationConfig" sheetId="18" r:id="Rc0d18afb71f241f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InjectorPool" sheetId="19" r:id="R48586e5b60d143e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleReward" sheetId="20" r:id="Rc0dd1101f1d74f57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResonanceBalance" sheetId="21" r:id="R33d9aaefca5c4866"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanetBattle" sheetId="22" r:id="Rd36380ed3d6a4659"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingConfig" sheetId="23" r:id="Recdc977ced8f4b83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingResult" sheetId="24" r:id="Raafc5d4d20d84fc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingRecipe" sheetId="25" r:id="R3cbc87f5427f4a1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BreedingCombinationPublic" sheetId="26" r:id="Rec7430fa07764765"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyContent" sheetId="27" r:id="R11200e515fc141f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameReward" sheetId="2" r:id="R524083d57c334d82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSpec" sheetId="4" r:id="R921585b468554f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopProduct" sheetId="5" r:id="R07c22c5be6a6406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GachaPool" sheetId="6" r:id="Rab5e7de633294638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienUpgradeCost" sheetId="7" r:id="R0ab39e38f98d4128"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienLevelStat" sheetId="8" r:id="Rcb79636c56a6466b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterSpec" sheetId="9" r:id="R91edbe3ba1454da7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="10" r:id="Rd94c62f5b7e34c2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="11" r:id="R5dd1f1cf06a94270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldLimitBalance" sheetId="12" r:id="R733d454e8cd64c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonBalance" sheetId="13" r:id="Rf3a5e05136f24550"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MergeRule" sheetId="14" r:id="R68e491a317f243d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicChoiceBalance" sheetId="15" r:id="R665eb31f8f4e4bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SummonPool" sheetId="16" r:id="R6713631ba24149ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MutationSpec" sheetId="17" r:id="R7aa6a0a0f7c64f28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MutationConfig" sheetId="18" r:id="Rb6bf4df4f14141b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InjectorPool" sheetId="19" r:id="R633f30a3e3934a0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleReward" sheetId="20" r:id="Raa14fd40d5174b5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResonanceBalance" sheetId="21" r:id="R751e52a2db764a2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanetBattle" sheetId="22" r:id="R3d47ddddd8a4402a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingConfig" sheetId="23" r:id="R5ca46aa4be854056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingResult" sheetId="24" r:id="Rd8d28448129b493c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MythicBreedingRecipe" sheetId="25" r:id="R7f5967ff8c5f499f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BreedingCombinationPublic" sheetId="26" r:id="Rd8701b1d83164dfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyContent" sheetId="27" r:id="R5a0af78a4bc5425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyBattleStage" sheetId="28" r:id="R201e1dc3a5cb48bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -161,11 +162,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.00"/>
     <x:numFmt numFmtId="202" formatCode="#,##0"/>
     <x:numFmt numFmtId="203" formatCode="0.0000"/>
+    <x:numFmt numFmtId="204" formatCode="0%"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -209,7 +211,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="22">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -299,6 +301,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF3B5B7A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3B5B7A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFB7DEE8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -536,7 +553,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="156">
+  <x:cellXfs count="180">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,6 +941,90 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -974,6 +1075,30 @@
     <x:tableColumn id="3" name="repeatReward"/>
     <x:tableColumn id="4" name="firstClearReward"/>
     <x:tableColumn id="5" name="enabled"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DailyBattleStageTable" displayName="DailyBattleStageTable" ref="A1:O51" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:O51"/>
+  <x:tableColumns count="15">
+    <x:tableColumn id="1" name="contentType"/>
+    <x:tableColumn id="2" name="mapId"/>
+    <x:tableColumn id="3" name="stage"/>
+    <x:tableColumn id="4" name="wave"/>
+    <x:tableColumn id="5" name="timeLimitSeconds"/>
+    <x:tableColumn id="6" name="monsterSpecId"/>
+    <x:tableColumn id="7" name="spawnCount"/>
+    <x:tableColumn id="8" name="spawnIntervalSeconds"/>
+    <x:tableColumn id="9" name="hpMultiplier"/>
+    <x:tableColumn id="10" name="moveSpeedMultiplier"/>
+    <x:tableColumn id="11" name="lanePolicy"/>
+    <x:tableColumn id="12" name="boss"/>
+    <x:tableColumn id="13" name="statusEffectType"/>
+    <x:tableColumn id="14" name="statusEffectValue"/>
+    <x:tableColumn id="15" name="enabled"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -3137,7 +3262,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R209cfc00e12d4f21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R026368c862d943ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19820,7 +19945,2433 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra244cf70bf03403a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b50efcd961e48c9"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="9" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="20" customHeight="1">
+      <x:c r="A1" s="159" t="str">
+        <x:v>contentType</x:v>
+      </x:c>
+      <x:c r="B1" s="159" t="str">
+        <x:v>mapId</x:v>
+      </x:c>
+      <x:c r="C1" s="159" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="D1" s="159" t="str">
+        <x:v>wave</x:v>
+      </x:c>
+      <x:c r="E1" s="159" t="str">
+        <x:v>timeLimitSeconds</x:v>
+      </x:c>
+      <x:c r="F1" s="159" t="str">
+        <x:v>monsterSpecId</x:v>
+      </x:c>
+      <x:c r="G1" s="159" t="str">
+        <x:v>spawnCount</x:v>
+      </x:c>
+      <x:c r="H1" s="159" t="str">
+        <x:v>spawnIntervalSeconds</x:v>
+      </x:c>
+      <x:c r="I1" s="159" t="str">
+        <x:v>hpMultiplier</x:v>
+      </x:c>
+      <x:c r="J1" s="159" t="str">
+        <x:v>moveSpeedMultiplier</x:v>
+      </x:c>
+      <x:c r="K1" s="159" t="str">
+        <x:v>lanePolicy</x:v>
+      </x:c>
+      <x:c r="L1" s="159" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="M1" s="159" t="str">
+        <x:v>statusEffectType</x:v>
+      </x:c>
+      <x:c r="N1" s="159" t="str">
+        <x:v>statusEffectValue</x:v>
+      </x:c>
+      <x:c r="O1" s="159" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="20" customHeight="1">
+      <x:c r="A2" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B2" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C2" s="174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="174" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F2" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G2" s="174" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H2" s="176" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I2" s="176" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J2" s="176" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="K2" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L2" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M2" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N2" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O2" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="20" customHeight="1">
+      <x:c r="A3" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B3" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C3" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="175" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E3" s="175" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F3" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G3" s="175" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H3" s="177" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I3" s="177" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="J3" s="177" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="K3" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L3" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M3" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N3" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O3" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="20" customHeight="1">
+      <x:c r="A4" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B4" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C4" s="174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" s="174" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E4" s="174" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F4" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G4" s="174" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H4" s="176" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I4" s="176" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="J4" s="176" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="K4" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L4" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M4" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N4" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O4" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="20" customHeight="1">
+      <x:c r="A5" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B5" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C5" s="175" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="175" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F5" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G5" s="175" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H5" s="177" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="I5" s="177" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="J5" s="177" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="K5" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L5" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N5" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O5" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="20" customHeight="1">
+      <x:c r="A6" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B6" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C6" s="174" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="174" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" s="174" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F6" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G6" s="174" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H6" s="176" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="I6" s="176" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="J6" s="176" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="K6" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L6" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N6" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="20" customHeight="1">
+      <x:c r="A7" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B7" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C7" s="175" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="175" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="175" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F7" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G7" s="175" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H7" s="177" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="I7" s="177" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J7" s="177" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="K7" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L7" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N7" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="20" customHeight="1">
+      <x:c r="A8" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B8" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C8" s="174" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D8" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E8" s="174" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F8" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G8" s="174" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H8" s="176" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="I8" s="176" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="J8" s="176" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="K8" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L8" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N8" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="20" customHeight="1">
+      <x:c r="A9" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B9" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C9" s="175" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D9" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="175" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F9" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G9" s="175" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H9" s="177" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="I9" s="177" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="J9" s="177" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L9" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N9" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O9" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="20" customHeight="1">
+      <x:c r="A10" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B10" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C10" s="174" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D10" s="174" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E10" s="174" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F10" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G10" s="174" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H10" s="176" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="I10" s="176" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="J10" s="176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K10" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L10" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N10" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="20" customHeight="1">
+      <x:c r="A11" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B11" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C11" s="175" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="175" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="175" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F11" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G11" s="175" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H11" s="177" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="I11" s="177" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="J11" s="177" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L11" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N11" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="20" customHeight="1">
+      <x:c r="A12" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B12" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C12" s="174" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D12" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E12" s="174" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F12" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G12" s="174" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H12" s="176" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="I12" s="176" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="J12" s="176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L12" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N12" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="20" customHeight="1">
+      <x:c r="A13" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B13" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C13" s="175" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D13" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E13" s="175" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F13" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G13" s="175" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H13" s="177" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="I13" s="177" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J13" s="177" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K13" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L13" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N13" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="20" customHeight="1">
+      <x:c r="A14" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B14" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C14" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D14" s="174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="174" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F14" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G14" s="174" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H14" s="176" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I14" s="176" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="J14" s="176" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K14" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L14" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N14" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="20" customHeight="1">
+      <x:c r="A15" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B15" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C15" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D15" s="175" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E15" s="175" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F15" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G15" s="175" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H15" s="177" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I15" s="177" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="J15" s="177" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K15" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L15" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N15" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="20" customHeight="1">
+      <x:c r="A16" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B16" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C16" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D16" s="174" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="174" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F16" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G16" s="174" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H16" s="176" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I16" s="176" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="J16" s="176" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K16" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L16" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N16" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="20" customHeight="1">
+      <x:c r="A17" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B17" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C17" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D17" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E17" s="175" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F17" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G17" s="175" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H17" s="177" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I17" s="177" t="n">
+        <x:v>1.55</x:v>
+      </x:c>
+      <x:c r="J17" s="177" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K17" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L17" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N17" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="20" customHeight="1">
+      <x:c r="A18" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B18" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C18" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D18" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E18" s="174" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F18" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G18" s="174" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H18" s="176" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I18" s="176" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="J18" s="176" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K18" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L18" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N18" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="20" customHeight="1">
+      <x:c r="A19" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B19" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C19" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D19" s="175" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E19" s="175" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F19" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G19" s="175" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H19" s="177" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I19" s="177" t="n">
+        <x:v>1.65</x:v>
+      </x:c>
+      <x:c r="J19" s="177" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K19" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L19" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N19" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O19" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="20" customHeight="1">
+      <x:c r="A20" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B20" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C20" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D20" s="174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E20" s="174" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F20" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G20" s="174" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H20" s="176" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I20" s="176" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="J20" s="176" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K20" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L20" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N20" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O20" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="20" customHeight="1">
+      <x:c r="A21" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B21" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C21" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D21" s="175" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E21" s="175" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F21" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G21" s="175" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H21" s="177" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I21" s="177" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="J21" s="177" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K21" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L21" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N21" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O21" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="20" customHeight="1">
+      <x:c r="A22" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B22" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C22" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D22" s="174" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E22" s="174" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F22" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G22" s="174" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H22" s="176" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I22" s="176" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="J22" s="176" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K22" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L22" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N22" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O22" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="20" customHeight="1">
+      <x:c r="A23" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B23" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C23" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D23" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E23" s="175" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F23" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G23" s="175" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H23" s="177" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I23" s="177" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="J23" s="177" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K23" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L23" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M23" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N23" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O23" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="20" customHeight="1">
+      <x:c r="A24" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B24" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C24" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D24" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E24" s="174" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F24" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G24" s="174" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H24" s="176" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I24" s="176" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J24" s="176" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K24" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L24" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M24" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N24" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O24" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="20" customHeight="1">
+      <x:c r="A25" s="169" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B25" s="169" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C25" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D25" s="175" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E25" s="175" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F25" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G25" s="175" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H25" s="177" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I25" s="177" t="n">
+        <x:v>2.05</x:v>
+      </x:c>
+      <x:c r="J25" s="177" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K25" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L25" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M25" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N25" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O25" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="20" customHeight="1">
+      <x:c r="A26" s="168" t="str">
+        <x:v>CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="B26" s="168" t="str">
+        <x:v>DAILY_CULTIVATION_ZONE</x:v>
+      </x:c>
+      <x:c r="C26" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D26" s="174" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E26" s="174" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F26" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G26" s="174" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H26" s="176" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I26" s="176" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="J26" s="176" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K26" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L26" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N26" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O26" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="20" customHeight="1">
+      <x:c r="A27" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B27" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C27" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D27" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="175" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F27" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G27" s="175" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H27" s="177" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I27" s="177" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J27" s="177" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="K27" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L27" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" s="172" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N27" s="179" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O27" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="20" customHeight="1">
+      <x:c r="A28" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B28" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C28" s="174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D28" s="174" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E28" s="174" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F28" s="174" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="G28" s="174" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H28" s="176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I28" s="176" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="J28" s="176" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="K28" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L28" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="170" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N28" s="178" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="O28" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="20" customHeight="1">
+      <x:c r="A29" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B29" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C29" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D29" s="175" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E29" s="175" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F29" s="175" t="str">
+        <x:v>WAVE_BOSS</x:v>
+      </x:c>
+      <x:c r="G29" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="177" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="177" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="J29" s="177" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="K29" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L29" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M29" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N29" s="179" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="O29" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="20" customHeight="1">
+      <x:c r="A30" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B30" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C30" s="174" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D30" s="174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" s="174" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F30" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G30" s="174" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H30" s="176" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="I30" s="176" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="J30" s="176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K30" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L30" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M30" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N30" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O30" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="20" customHeight="1">
+      <x:c r="A31" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B31" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C31" s="175" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D31" s="175" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E31" s="175" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F31" s="175" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="G31" s="175" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H31" s="177" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="I31" s="177" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="J31" s="177" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K31" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L31" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M31" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N31" s="179" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="O31" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="20" customHeight="1">
+      <x:c r="A32" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B32" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C32" s="174" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D32" s="174" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E32" s="174" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F32" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G32" s="174" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H32" s="176" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="I32" s="176" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="J32" s="176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K32" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L32" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M32" s="170" t="str">
+        <x:v>ATTACK_DOWN</x:v>
+      </x:c>
+      <x:c r="N32" s="178" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="O32" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="20" customHeight="1">
+      <x:c r="A33" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B33" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C33" s="175" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D33" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E33" s="175" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F33" s="175" t="str">
+        <x:v>WAVE_BOSS</x:v>
+      </x:c>
+      <x:c r="G33" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H33" s="177" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" s="177" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J33" s="177" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="K33" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L33" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M33" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N33" s="179" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="O33" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="20" customHeight="1">
+      <x:c r="A34" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B34" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C34" s="174" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D34" s="174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34" s="174" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F34" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G34" s="174" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H34" s="176" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="I34" s="176" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="J34" s="176" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K34" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L34" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="170" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N34" s="178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O34" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="20" customHeight="1">
+      <x:c r="A35" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B35" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C35" s="175" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D35" s="175" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E35" s="175" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F35" s="175" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="G35" s="175" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H35" s="177" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="I35" s="177" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="J35" s="177" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K35" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L35" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N35" s="179" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="O35" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="20" customHeight="1">
+      <x:c r="A36" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B36" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C36" s="174" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D36" s="174" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E36" s="174" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F36" s="174" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G36" s="174" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H36" s="176" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="I36" s="176" t="n">
+        <x:v>1.55</x:v>
+      </x:c>
+      <x:c r="J36" s="176" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K36" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L36" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" s="170" t="str">
+        <x:v>ATTACK_DOWN</x:v>
+      </x:c>
+      <x:c r="N36" s="178" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="O36" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="20" customHeight="1">
+      <x:c r="A37" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B37" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C37" s="175" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D37" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E37" s="175" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F37" s="175" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="G37" s="175" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H37" s="177" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="I37" s="177" t="n">
+        <x:v>1.65</x:v>
+      </x:c>
+      <x:c r="J37" s="177" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K37" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L37" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N37" s="179" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="O37" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="20" customHeight="1">
+      <x:c r="A38" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B38" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C38" s="174" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D38" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E38" s="174" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F38" s="174" t="str">
+        <x:v>WAVE_BOSS</x:v>
+      </x:c>
+      <x:c r="G38" s="174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H38" s="176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="176" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="J38" s="176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K38" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L38" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M38" s="170" t="str">
+        <x:v>ATTACK_DOWN</x:v>
+      </x:c>
+      <x:c r="N38" s="178" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="O38" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="20" customHeight="1">
+      <x:c r="A39" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B39" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C39" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D39" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E39" s="175" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F39" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G39" s="175" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H39" s="177" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="I39" s="177" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="J39" s="177" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K39" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L39" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N39" s="179" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="O39" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="20" customHeight="1">
+      <x:c r="A40" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B40" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C40" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D40" s="174" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E40" s="174" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F40" s="174" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="G40" s="174" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H40" s="176" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="I40" s="176" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="J40" s="176" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K40" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L40" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="170" t="str">
+        <x:v>ATTACK_DOWN</x:v>
+      </x:c>
+      <x:c r="N40" s="178" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="O40" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="20" customHeight="1">
+      <x:c r="A41" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B41" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C41" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D41" s="175" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E41" s="175" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F41" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G41" s="175" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H41" s="177" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="I41" s="177" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="J41" s="177" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K41" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L41" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M41" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N41" s="179" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="O41" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="20" customHeight="1">
+      <x:c r="A42" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B42" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C42" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D42" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E42" s="174" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F42" s="174" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="G42" s="174" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H42" s="176" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="I42" s="176" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="J42" s="176" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K42" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L42" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M42" s="170" t="str">
+        <x:v>ATTACK_DOWN</x:v>
+      </x:c>
+      <x:c r="N42" s="178" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="O42" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="20" customHeight="1">
+      <x:c r="A43" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B43" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C43" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D43" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E43" s="175" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F43" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G43" s="175" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H43" s="177" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="I43" s="177" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J43" s="177" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K43" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L43" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M43" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N43" s="179" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="O43" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="20" customHeight="1">
+      <x:c r="A44" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B44" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C44" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D44" s="174" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E44" s="174" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F44" s="174" t="str">
+        <x:v>WAVE_BOSS</x:v>
+      </x:c>
+      <x:c r="G44" s="174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H44" s="176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I44" s="176" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J44" s="176" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="K44" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L44" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M44" s="170" t="str">
+        <x:v>ATTACK_DOWN</x:v>
+      </x:c>
+      <x:c r="N44" s="178" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="O44" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="20" customHeight="1">
+      <x:c r="A45" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B45" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C45" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D45" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E45" s="175" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F45" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G45" s="175" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H45" s="177" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I45" s="177" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J45" s="177" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="K45" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L45" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M45" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N45" s="179" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="O45" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="20" customHeight="1">
+      <x:c r="A46" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B46" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C46" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D46" s="174" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E46" s="174" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F46" s="174" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="G46" s="174" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H46" s="176" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I46" s="176" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="J46" s="176" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="K46" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L46" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M46" s="170" t="str">
+        <x:v>ATTACK_DOWN</x:v>
+      </x:c>
+      <x:c r="N46" s="178" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="O46" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="20" customHeight="1">
+      <x:c r="A47" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B47" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C47" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D47" s="175" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E47" s="175" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F47" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G47" s="175" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H47" s="177" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I47" s="177" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="J47" s="177" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="K47" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L47" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M47" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N47" s="179" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="O47" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="20" customHeight="1">
+      <x:c r="A48" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B48" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C48" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D48" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E48" s="174" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F48" s="174" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="G48" s="174" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H48" s="176" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I48" s="176" t="n">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="J48" s="176" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="K48" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L48" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M48" s="170" t="str">
+        <x:v>ATTACK_DOWN</x:v>
+      </x:c>
+      <x:c r="N48" s="178" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="O48" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="20" customHeight="1">
+      <x:c r="A49" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B49" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C49" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D49" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E49" s="175" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F49" s="175" t="str">
+        <x:v>NORMAL_MONSTER</x:v>
+      </x:c>
+      <x:c r="G49" s="175" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H49" s="177" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I49" s="177" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="J49" s="177" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="K49" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L49" s="173" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M49" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N49" s="179" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="O49" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="20" customHeight="1">
+      <x:c r="A50" s="168" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B50" s="168" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C50" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D50" s="174" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E50" s="174" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F50" s="174" t="str">
+        <x:v>ELITE_MONSTER</x:v>
+      </x:c>
+      <x:c r="G50" s="174" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H50" s="176" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I50" s="176" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="J50" s="176" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="K50" s="170" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L50" s="171" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M50" s="170" t="str">
+        <x:v>ATTACK_DOWN</x:v>
+      </x:c>
+      <x:c r="N50" s="178" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="O50" s="171" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="20" customHeight="1">
+      <x:c r="A51" s="169" t="str">
+        <x:v>MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="B51" s="169" t="str">
+        <x:v>DAILY_MUTATION_LAB</x:v>
+      </x:c>
+      <x:c r="C51" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D51" s="175" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E51" s="175" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F51" s="175" t="str">
+        <x:v>WAVE_BOSS</x:v>
+      </x:c>
+      <x:c r="G51" s="175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H51" s="177" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I51" s="177" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J51" s="177" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K51" s="172" t="str">
+        <x:v>PLAYER_ONE_ONLY</x:v>
+      </x:c>
+      <x:c r="L51" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M51" s="172" t="str">
+        <x:v>ATTACK_SPEED_DOWN</x:v>
+      </x:c>
+      <x:c r="N51" s="179" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="O51" s="173" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2913a4004ab04699"/>
   </x:tableParts>
 </x:worksheet>
 </file>
